--- a/OMOP Analysis/Results/Output_visits_OMOP-Adjusted.xlsx
+++ b/OMOP Analysis/Results/Output_visits_OMOP-Adjusted.xlsx
@@ -414,37 +414,37 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>22.57</v>
+        <v>26.18</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2">
         <v>444</v>
       </c>
       <c r="D2">
-        <v>24.53</v>
+        <v>25.99</v>
       </c>
       <c r="E2">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G2">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H2">
-        <v>16738</v>
+        <v>13178</v>
       </c>
       <c r="I2">
-        <v>0.19</v>
+        <v>0.23</v>
       </c>
       <c r="J2">
-        <v>22.2</v>
+        <v>25.74</v>
       </c>
       <c r="K2">
-        <v>22.94</v>
+        <v>26.63</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/Output_visits_OMOP-Adjusted.xlsx
+++ b/OMOP Analysis/Results/Output_visits_OMOP-Adjusted.xlsx
@@ -414,7 +414,7 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>26.18</v>
+        <v>30.65</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -423,28 +423,28 @@
         <v>444</v>
       </c>
       <c r="D2">
-        <v>25.99</v>
+        <v>26.75</v>
       </c>
       <c r="E2">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F2">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G2">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H2">
-        <v>13178</v>
+        <v>14956</v>
       </c>
       <c r="I2">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="J2">
-        <v>25.74</v>
+        <v>30.22</v>
       </c>
       <c r="K2">
-        <v>26.63</v>
+        <v>31.08</v>
       </c>
     </row>
   </sheetData>
@@ -516,7 +516,7 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>27.04</v>
+        <v>30.97</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -525,28 +525,28 @@
         <v>444</v>
       </c>
       <c r="D2">
-        <v>25.97</v>
+        <v>26.71</v>
       </c>
       <c r="E2">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G2">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H2">
-        <v>12761</v>
+        <v>14802</v>
       </c>
       <c r="I2">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="J2">
-        <v>26.59</v>
+        <v>30.54</v>
       </c>
       <c r="K2">
-        <v>27.49</v>
+        <v>31.4</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/Output_visits_OMOP-Adjusted.xlsx
+++ b/OMOP Analysis/Results/Output_visits_OMOP-Adjusted.xlsx
@@ -414,37 +414,37 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>30.65</v>
+        <v>213.65</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2">
-        <v>444</v>
+        <v>6351</v>
       </c>
       <c r="D2">
-        <v>26.75</v>
+        <v>194.38</v>
       </c>
       <c r="E2">
-        <v>24</v>
+        <v>162</v>
       </c>
       <c r="F2">
-        <v>13</v>
+        <v>90</v>
       </c>
       <c r="G2">
-        <v>40</v>
+        <v>277</v>
       </c>
       <c r="H2">
         <v>14956</v>
       </c>
       <c r="I2">
-        <v>0.22</v>
+        <v>1.59</v>
       </c>
       <c r="J2">
-        <v>30.22</v>
+        <v>210.53</v>
       </c>
       <c r="K2">
-        <v>31.08</v>
+        <v>216.76</v>
       </c>
     </row>
   </sheetData>
@@ -516,37 +516,37 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>30.97</v>
+        <v>120.27</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2">
-        <v>444</v>
+        <v>1747</v>
       </c>
       <c r="D2">
-        <v>26.71</v>
+        <v>112.98</v>
       </c>
       <c r="E2">
-        <v>24</v>
+        <v>90.5</v>
       </c>
       <c r="F2">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="G2">
-        <v>40</v>
+        <v>157</v>
       </c>
       <c r="H2">
-        <v>14802</v>
+        <v>14808</v>
       </c>
       <c r="I2">
-        <v>0.22</v>
+        <v>0.93</v>
       </c>
       <c r="J2">
-        <v>30.54</v>
+        <v>118.45</v>
       </c>
       <c r="K2">
-        <v>31.4</v>
+        <v>122.09</v>
       </c>
     </row>
   </sheetData>
